--- a/GourmetProject/GameConfig/Datas/reward_slot.xlsx
+++ b/GourmetProject/GameConfig/Datas/reward_slot.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,100 +466,112 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>##comment</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>奖励槽ID</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>槽组ID</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>奖励类型</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>候选数量</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>槽权重</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>使用的奖励池ID</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>隐藏分偏移</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>兜底金币数量</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>##type</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>RewardKind</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>int</t>
         </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>slot_main_dish</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>main_dish</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>DishChoice</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>pool_dish</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>40</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>slot_main_passive</t>
+          <t>slot_main_dish</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>main_passive</t>
+          <t>main_dish</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PassiveItemChoice</t>
+          <t>DishChoice</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -570,31 +582,31 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>pool_passive</t>
+          <t>pool_dish</t>
         </is>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>slot_main_fragment</t>
+          <t>slot_main_passive</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>main_fragment</t>
+          <t>main_passive</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>FragmentChoice</t>
+          <t>PassiveItemChoice</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -605,56 +617,56 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>pool_fragment</t>
+          <t>pool_passive</t>
         </is>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>slot_main_dish_late</t>
+          <t>slot_main_fragment</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>main_dish_or_passive</t>
+          <t>main_fragment</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>DishChoice</t>
+          <t>FragmentChoice</t>
         </is>
       </c>
       <c r="E6" t="n">
         <v>3</v>
       </c>
       <c r="F6" t="n">
-        <v>55</v>
+        <v>1</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>pool_dish</t>
+          <t>pool_fragment</t>
         </is>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>slot_main_passive_late</t>
+          <t>slot_main_dish_late</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -664,37 +676,37 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>PassiveItemChoice</t>
+          <t>DishChoice</t>
         </is>
       </c>
       <c r="E7" t="n">
         <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>pool_passive</t>
+          <t>pool_dish</t>
         </is>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>slot_boss_passive</t>
+          <t>slot_main_passive_late</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>main_boss</t>
+          <t>main_dish_or_passive</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -706,25 +718,25 @@
         <v>3</v>
       </c>
       <c r="F8" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>pool_passive_boss</t>
+          <t>pool_passive</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>slot_boss_active</t>
+          <t>slot_boss_passive</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -734,37 +746,37 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ActiveItemGrant</t>
+          <t>PassiveItemChoice</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F9" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>pool_active</t>
+          <t>pool_passive_boss</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I9" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>slot_extra_active</t>
+          <t>slot_boss_active</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>extra_mixed</t>
+          <t>main_boss</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -776,7 +788,7 @@
         <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -787,14 +799,14 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>slot_extra_gold</t>
+          <t>slot_extra_active</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -804,20 +816,55 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>ActiveItemGrant</t>
         </is>
       </c>
       <c r="E11" t="n">
         <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>55</v>
-      </c>
-      <c r="G11" t="inlineStr"/>
+        <v>45</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>pool_active</t>
+        </is>
+      </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>slot_extra_gold</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>extra_mixed</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>55</v>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
         <v>30</v>
       </c>
     </row>
